--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/12.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/12.xlsx
@@ -426,13 +426,13 @@
         <v>-8.455954858767733</v>
       </c>
       <c r="E2">
-        <v>-10.43023224031825</v>
+        <v>-10.08789964365793</v>
       </c>
       <c r="F2">
-        <v>2.713881398823579</v>
+        <v>2.5536883970006</v>
       </c>
       <c r="G2">
-        <v>-16.44292838171043</v>
+        <v>-16.02969711708442</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.002680910551506</v>
       </c>
       <c r="E3">
-        <v>-10.51001542986821</v>
+        <v>-11.63073873981657</v>
       </c>
       <c r="F3">
-        <v>2.751293784203616</v>
+        <v>2.674084972058286</v>
       </c>
       <c r="G3">
-        <v>-15.52168929693953</v>
+        <v>-15.43697585644709</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.469650349896101</v>
       </c>
       <c r="E4">
-        <v>-10.97510864686781</v>
+        <v>-12.41685027295746</v>
       </c>
       <c r="F4">
-        <v>2.480420956957789</v>
+        <v>2.382932054057121</v>
       </c>
       <c r="G4">
-        <v>-15.08269912080531</v>
+        <v>-15.1833511570265</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.935892117848817</v>
       </c>
       <c r="E5">
-        <v>-11.18448448938639</v>
+        <v>-12.22427001703649</v>
       </c>
       <c r="F5">
-        <v>3.101539119250886</v>
+        <v>2.37348369546079</v>
       </c>
       <c r="G5">
-        <v>-14.9470644124355</v>
+        <v>-14.65420544329966</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.412115826739933</v>
       </c>
       <c r="E6">
-        <v>-11.79074120610559</v>
+        <v>-12.93677003265612</v>
       </c>
       <c r="F6">
-        <v>3.065505137229108</v>
+        <v>2.748076405211143</v>
       </c>
       <c r="G6">
-        <v>-14.20144489481961</v>
+        <v>-13.92275965806893</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.931333906862638</v>
       </c>
       <c r="E7">
-        <v>-13.97484028402907</v>
+        <v>-13.98950112000571</v>
       </c>
       <c r="F7">
-        <v>2.920887099313564</v>
+        <v>2.746209265085233</v>
       </c>
       <c r="G7">
-        <v>-13.79693873861711</v>
+        <v>-13.52048829923642</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.496914024575367</v>
       </c>
       <c r="E8">
-        <v>-13.80935557879128</v>
+        <v>-14.89383796671918</v>
       </c>
       <c r="F8">
-        <v>2.673955746743449</v>
+        <v>2.9163111977805</v>
       </c>
       <c r="G8">
-        <v>-12.6789017265681</v>
+        <v>-13.42199795953667</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.113479903551942</v>
       </c>
       <c r="E9">
-        <v>-14.00107196675669</v>
+        <v>-15.41855468549802</v>
       </c>
       <c r="F9">
-        <v>3.399714936092985</v>
+        <v>2.960690153018081</v>
       </c>
       <c r="G9">
-        <v>-13.79839683947125</v>
+        <v>-13.15318916957417</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.771663707434721</v>
       </c>
       <c r="E10">
-        <v>-15.83220622702829</v>
+        <v>-15.88748546976176</v>
       </c>
       <c r="F10">
-        <v>3.623360880970407</v>
+        <v>3.046576942075139</v>
       </c>
       <c r="G10">
-        <v>-12.71553961078749</v>
+        <v>-12.48821424700548</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.459561815168705</v>
       </c>
       <c r="E11">
-        <v>-14.81148393935915</v>
+        <v>-16.53899973028761</v>
       </c>
       <c r="F11">
-        <v>3.502483852819097</v>
+        <v>3.747950651821064</v>
       </c>
       <c r="G11">
-        <v>-11.69070879138581</v>
+        <v>-12.30622576842045</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.168185497026033</v>
       </c>
       <c r="E12">
-        <v>-16.45930375817548</v>
+        <v>-17.07432375079006</v>
       </c>
       <c r="F12">
-        <v>4.158361968068467</v>
+        <v>3.803356833924711</v>
       </c>
       <c r="G12">
-        <v>-11.1208054384748</v>
+        <v>-11.84689658654916</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.881686490220285</v>
       </c>
       <c r="E13">
-        <v>-18.1863793087035</v>
+        <v>-17.70425792527211</v>
       </c>
       <c r="F13">
-        <v>4.516273015061245</v>
+        <v>3.876009625354645</v>
       </c>
       <c r="G13">
-        <v>-11.57027122728087</v>
+        <v>-11.46014610431082</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.598920570035375</v>
       </c>
       <c r="E14">
-        <v>-17.07606809954649</v>
+        <v>-18.0877197736822</v>
       </c>
       <c r="F14">
-        <v>4.471872522271191</v>
+        <v>3.874125917880679</v>
       </c>
       <c r="G14">
-        <v>-10.46919752821261</v>
+        <v>-11.17329054236225</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.308860419992282</v>
       </c>
       <c r="E15">
-        <v>-19.46176820838847</v>
+        <v>-19.86778199429239</v>
       </c>
       <c r="F15">
-        <v>4.412543192147885</v>
+        <v>4.158958392598484</v>
       </c>
       <c r="G15">
-        <v>-10.54606959732565</v>
+        <v>-11.0846414043987</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.011287717898057</v>
       </c>
       <c r="E16">
-        <v>-19.02562702753426</v>
+        <v>-20.78065369027838</v>
       </c>
       <c r="F16">
-        <v>4.682688712814054</v>
+        <v>4.473086908883695</v>
       </c>
       <c r="G16">
-        <v>-9.329593155096411</v>
+        <v>-10.66358443286084</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.702049611757628</v>
       </c>
       <c r="E17">
-        <v>-19.81648152800811</v>
+        <v>-21.25819823482981</v>
       </c>
       <c r="F17">
-        <v>5.144294791289273</v>
+        <v>4.805262237406297</v>
       </c>
       <c r="G17">
-        <v>-9.682437897329962</v>
+        <v>-10.66166161946948</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.381890514156852</v>
       </c>
       <c r="E18">
-        <v>-20.22716352344113</v>
+        <v>-22.32798656109047</v>
       </c>
       <c r="F18">
-        <v>5.119766832492379</v>
+        <v>4.823212959024962</v>
       </c>
       <c r="G18">
-        <v>-9.161479478640853</v>
+        <v>-10.13350798868727</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.055312358482859</v>
       </c>
       <c r="E19">
-        <v>-23.04343120353941</v>
+        <v>-23.69214619963233</v>
       </c>
       <c r="F19">
-        <v>5.374209820671081</v>
+        <v>5.076966745524534</v>
       </c>
       <c r="G19">
-        <v>-8.663419900760399</v>
+        <v>-9.759619339677045</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.725948485952554</v>
       </c>
       <c r="E20">
-        <v>-22.71929797890449</v>
+        <v>-23.63624812841146</v>
       </c>
       <c r="F20">
-        <v>5.468993275634206</v>
+        <v>5.371545791103678</v>
       </c>
       <c r="G20">
-        <v>-8.694949863187274</v>
+        <v>-10.23565467618687</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.406060191419312</v>
       </c>
       <c r="E21">
-        <v>-22.72657025193427</v>
+        <v>-24.41252485713517</v>
       </c>
       <c r="F21">
-        <v>5.729912440167994</v>
+        <v>5.42426640608745</v>
       </c>
       <c r="G21">
-        <v>-9.264793168972684</v>
+        <v>-9.233652207489884</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.101676859134042</v>
       </c>
       <c r="E22">
-        <v>-23.31248038637313</v>
+        <v>-25.06778531427602</v>
       </c>
       <c r="F22">
-        <v>5.407738819666794</v>
+        <v>5.480527463350787</v>
       </c>
       <c r="G22">
-        <v>-8.797720518644152</v>
+        <v>-8.984144652289483</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.8242204821904202</v>
       </c>
       <c r="E23">
-        <v>-25.25403192292663</v>
+        <v>-25.28008501756728</v>
       </c>
       <c r="F23">
-        <v>6.063562262667579</v>
+        <v>5.212814029379237</v>
       </c>
       <c r="G23">
-        <v>-8.715713114920398</v>
+        <v>-8.612717935428682</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.5771579108996577</v>
       </c>
       <c r="E24">
-        <v>-25.05157948368653</v>
+        <v>-26.05265292857791</v>
       </c>
       <c r="F24">
-        <v>5.86473089170842</v>
+        <v>5.680551683369978</v>
       </c>
       <c r="G24">
-        <v>-7.608556380954848</v>
+        <v>-8.77295238470826</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.364630518197482</v>
       </c>
       <c r="E25">
-        <v>-26.07358926686637</v>
+        <v>-26.51735574371297</v>
       </c>
       <c r="F25">
-        <v>5.532179484384947</v>
+        <v>5.185557428357522</v>
       </c>
       <c r="G25">
-        <v>-7.997862782147888</v>
+        <v>-8.452533090296336</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.1879548773377867</v>
       </c>
       <c r="E26">
-        <v>-24.73692388729487</v>
+        <v>-27.13467246219019</v>
       </c>
       <c r="F26">
-        <v>5.709413660418318</v>
+        <v>5.171529854758515</v>
       </c>
       <c r="G26">
-        <v>-7.832368987889512</v>
+        <v>-8.602789273748678</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.04643538001204397</v>
       </c>
       <c r="E27">
-        <v>-24.94243724328136</v>
+        <v>-27.51626121229279</v>
       </c>
       <c r="F27">
-        <v>5.40993896348863</v>
+        <v>5.443317199617033</v>
       </c>
       <c r="G27">
-        <v>-8.127853060711715</v>
+        <v>-7.646414788270582</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.05872507161426038</v>
       </c>
       <c r="E28">
-        <v>-26.50713053743124</v>
+        <v>-28.09017687242554</v>
       </c>
       <c r="F28">
-        <v>5.400638054289996</v>
+        <v>5.233422153626083</v>
       </c>
       <c r="G28">
-        <v>-7.245112015681377</v>
+        <v>-7.647661418812839</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.1286882641255608</v>
       </c>
       <c r="E29">
-        <v>-25.93150375423266</v>
+        <v>-28.02241722966096</v>
       </c>
       <c r="F29">
-        <v>5.391186382224054</v>
+        <v>4.934924930231698</v>
       </c>
       <c r="G29">
-        <v>-6.980011788410551</v>
+        <v>-7.441137162560527</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.1606621166804569</v>
       </c>
       <c r="E30">
-        <v>-26.6728436692919</v>
+        <v>-28.39173947011568</v>
       </c>
       <c r="F30">
-        <v>5.337720236577763</v>
+        <v>4.941773871918044</v>
       </c>
       <c r="G30">
-        <v>-7.195359056008531</v>
+        <v>-7.244900545369497</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.1529432232489574</v>
       </c>
       <c r="E31">
-        <v>-25.8335544183479</v>
+        <v>-29.01005918912784</v>
       </c>
       <c r="F31">
-        <v>5.186738680273914</v>
+        <v>4.650360846552401</v>
       </c>
       <c r="G31">
-        <v>-7.134471270654587</v>
+        <v>-7.021995172180244</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.1046943422969392</v>
       </c>
       <c r="E32">
-        <v>-26.7008778457345</v>
+        <v>-28.39248289494282</v>
       </c>
       <c r="F32">
-        <v>5.373805577378515</v>
+        <v>4.459162052842635</v>
       </c>
       <c r="G32">
-        <v>-6.804658517203837</v>
+        <v>-6.655274322444925</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.01512356619042301</v>
       </c>
       <c r="E33">
-        <v>-25.69485792615525</v>
+        <v>-29.15628753005807</v>
       </c>
       <c r="F33">
-        <v>5.55110602280411</v>
+        <v>4.70209239085723</v>
       </c>
       <c r="G33">
-        <v>-6.474963247259686</v>
+        <v>-6.667155821079082</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1123512191243676</v>
       </c>
       <c r="E34">
-        <v>-26.82966062249478</v>
+        <v>-29.02501490310855</v>
       </c>
       <c r="F34">
-        <v>4.84811202641831</v>
+        <v>4.882951502645251</v>
       </c>
       <c r="G34">
-        <v>-7.185908160588701</v>
+        <v>-6.075409673546527</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.2741372920705347</v>
       </c>
       <c r="E35">
-        <v>-24.19608440215305</v>
+        <v>-28.34395885042919</v>
       </c>
       <c r="F35">
-        <v>4.851862874018186</v>
+        <v>4.827487334823408</v>
       </c>
       <c r="G35">
-        <v>-5.974804630727976</v>
+        <v>-6.453544698634193</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.4659566440565611</v>
       </c>
       <c r="E36">
-        <v>-24.45241645191015</v>
+        <v>-27.57769551420965</v>
       </c>
       <c r="F36">
-        <v>5.131536276551355</v>
+        <v>4.916846640033001</v>
       </c>
       <c r="G36">
-        <v>-5.917869512684978</v>
+        <v>-6.282533095682499</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6819155719100027</v>
       </c>
       <c r="E37">
-        <v>-24.9410542239102</v>
+        <v>-27.67221845075142</v>
       </c>
       <c r="F37">
-        <v>5.171735289874409</v>
+        <v>4.728180993840997</v>
       </c>
       <c r="G37">
-        <v>-7.379513147231889</v>
+        <v>-6.171229221529567</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.9189167900177904</v>
       </c>
       <c r="E38">
-        <v>-23.45292122732221</v>
+        <v>-27.6630647729915</v>
       </c>
       <c r="F38">
-        <v>5.307367198204384</v>
+        <v>4.910116983252658</v>
       </c>
       <c r="G38">
-        <v>-6.716720807141368</v>
+        <v>-6.606693587093489</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.16940784891464</v>
       </c>
       <c r="E39">
-        <v>-24.6507821312066</v>
+        <v>-28.23313040622614</v>
       </c>
       <c r="F39">
-        <v>6.121392247791818</v>
+        <v>5.079882598782389</v>
       </c>
       <c r="G39">
-        <v>-6.430622361124218</v>
+        <v>-6.558603671725183</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.431674466387427</v>
       </c>
       <c r="E40">
-        <v>-23.43664063892888</v>
+        <v>-26.84293428588893</v>
       </c>
       <c r="F40">
-        <v>5.800042024489001</v>
+        <v>5.324835809994619</v>
       </c>
       <c r="G40">
-        <v>-6.542351786645503</v>
+        <v>-6.334703604846716</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.699178131687012</v>
       </c>
       <c r="E41">
-        <v>-22.98746668093735</v>
+        <v>-26.3768152256921</v>
       </c>
       <c r="F41">
-        <v>6.08722540589595</v>
+        <v>5.632456671963438</v>
       </c>
       <c r="G41">
-        <v>-7.013802655653331</v>
+        <v>-6.587872729336154</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.968712601168736</v>
       </c>
       <c r="E42">
-        <v>-23.11695550362285</v>
+        <v>-26.57537610592083</v>
       </c>
       <c r="F42">
-        <v>6.128347220505723</v>
+        <v>5.676825686792186</v>
       </c>
       <c r="G42">
-        <v>-7.097490073521467</v>
+        <v>-6.47555849702646</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.236366877134591</v>
       </c>
       <c r="E43">
-        <v>-23.29654036130844</v>
+        <v>-26.55060635357955</v>
       </c>
       <c r="F43">
-        <v>5.641166126836472</v>
+        <v>5.713577034984788</v>
       </c>
       <c r="G43">
-        <v>-7.354290743737144</v>
+        <v>-7.042447745307026</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.497926124036272</v>
       </c>
       <c r="E44">
-        <v>-20.06939548484486</v>
+        <v>-25.92000766528553</v>
       </c>
       <c r="F44">
-        <v>6.510837585074367</v>
+        <v>5.582201278370398</v>
       </c>
       <c r="G44">
-        <v>-6.653344982192093</v>
+        <v>-7.466450942115961</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.753264896016991</v>
       </c>
       <c r="E45">
-        <v>-22.5610232485266</v>
+        <v>-25.01202014581754</v>
       </c>
       <c r="F45">
-        <v>5.880090480091128</v>
+        <v>6.008056676475595</v>
       </c>
       <c r="G45">
-        <v>-7.637155782578199</v>
+        <v>-7.259677359755198</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.998067759523286</v>
       </c>
       <c r="E46">
-        <v>-21.30017889490118</v>
+        <v>-24.71104938074119</v>
       </c>
       <c r="F46">
-        <v>6.318190805144508</v>
+        <v>5.855130113509974</v>
       </c>
       <c r="G46">
-        <v>-7.417580414114911</v>
+        <v>-7.935304120255632</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.234651313454839</v>
       </c>
       <c r="E47">
-        <v>-21.02029813693231</v>
+        <v>-23.81350718775515</v>
       </c>
       <c r="F47">
-        <v>5.896271808937414</v>
+        <v>6.396120296930275</v>
       </c>
       <c r="G47">
-        <v>-8.463759292038123</v>
+        <v>-7.701617677277377</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.458362019030692</v>
       </c>
       <c r="E48">
-        <v>-19.54709178184575</v>
+        <v>-23.63328273552554</v>
       </c>
       <c r="F48">
-        <v>6.044186749116099</v>
+        <v>6.132122919127683</v>
       </c>
       <c r="G48">
-        <v>-9.167870581399898</v>
+        <v>-8.412866742351255</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.670629657040267</v>
       </c>
       <c r="E49">
-        <v>-19.56490075200662</v>
+        <v>-22.7559832945367</v>
       </c>
       <c r="F49">
-        <v>5.990970770425453</v>
+        <v>6.201076221736714</v>
       </c>
       <c r="G49">
-        <v>-8.180956911067254</v>
+        <v>-8.005355619124384</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.868616975027694</v>
       </c>
       <c r="E50">
-        <v>-19.83089732451659</v>
+        <v>-23.31144623675325</v>
       </c>
       <c r="F50">
-        <v>5.628944394175568</v>
+        <v>6.335467235697295</v>
       </c>
       <c r="G50">
-        <v>-8.694794523884102</v>
+        <v>-8.377868405735088</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.051430996002606</v>
       </c>
       <c r="E51">
-        <v>-17.61634690115946</v>
+        <v>-23.13905474108227</v>
       </c>
       <c r="F51">
-        <v>6.328348246237636</v>
+        <v>6.119130804782176</v>
       </c>
       <c r="G51">
-        <v>-8.055882664568495</v>
+        <v>-8.441536634078567</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.218903279159647</v>
       </c>
       <c r="E52">
-        <v>-17.98591210447668</v>
+        <v>-21.79772115198167</v>
       </c>
       <c r="F52">
-        <v>6.118385274119657</v>
+        <v>6.433542622719145</v>
       </c>
       <c r="G52">
-        <v>-9.453871124494881</v>
+        <v>-8.632566121182622</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.370163686763187</v>
       </c>
       <c r="E53">
-        <v>-19.424235637646</v>
+        <v>-21.68453783695744</v>
       </c>
       <c r="F53">
-        <v>5.266599924843009</v>
+        <v>6.197318747197616</v>
       </c>
       <c r="G53">
-        <v>-9.804823076899876</v>
+        <v>-9.357689988385973</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.508689884469702</v>
       </c>
       <c r="E54">
-        <v>-16.99383451531488</v>
+        <v>-21.14799277232549</v>
       </c>
       <c r="F54">
-        <v>5.407803432324212</v>
+        <v>6.411471601638955</v>
       </c>
       <c r="G54">
-        <v>-9.431092377937418</v>
+        <v>-9.363044625542345</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.632761658154972</v>
       </c>
       <c r="E55">
-        <v>-17.39013809314135</v>
+        <v>-20.89083838672608</v>
       </c>
       <c r="F55">
-        <v>6.156821521609554</v>
+        <v>6.445563890468572</v>
       </c>
       <c r="G55">
-        <v>-8.824316173793823</v>
+        <v>-9.111876636781997</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.747331578532754</v>
       </c>
       <c r="E56">
-        <v>-15.98733697643329</v>
+        <v>-20.18785337825162</v>
       </c>
       <c r="F56">
-        <v>5.928047982508803</v>
+        <v>6.210017619482532</v>
       </c>
       <c r="G56">
-        <v>-9.252817683533246</v>
+        <v>-9.222876359190064</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.851547113100898</v>
       </c>
       <c r="E57">
-        <v>-17.00707079980711</v>
+        <v>-20.01836913050802</v>
       </c>
       <c r="F57">
-        <v>5.796107279325703</v>
+        <v>6.399591156348005</v>
       </c>
       <c r="G57">
-        <v>-10.03868313439344</v>
+        <v>-9.679077869041199</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.948706087527143</v>
       </c>
       <c r="E58">
-        <v>-16.4267384281775</v>
+        <v>-19.8281894307328</v>
       </c>
       <c r="F58">
-        <v>6.532353599994681</v>
+        <v>6.595410583430585</v>
       </c>
       <c r="G58">
-        <v>-10.43608023307434</v>
+        <v>-10.070512027076</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.038741965367656</v>
       </c>
       <c r="E59">
-        <v>-15.25706536955471</v>
+        <v>-18.93926515124577</v>
       </c>
       <c r="F59">
-        <v>5.974415019513102</v>
+        <v>6.668424543048139</v>
       </c>
       <c r="G59">
-        <v>-9.432473461826117</v>
+        <v>-9.902424458066351</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.122875448694606</v>
       </c>
       <c r="E60">
-        <v>-15.27566760307862</v>
+        <v>-18.46020053134945</v>
       </c>
       <c r="F60">
-        <v>6.285256573944006</v>
+        <v>6.822182786886172</v>
       </c>
       <c r="G60">
-        <v>-10.11122658897441</v>
+        <v>-10.15362377576179</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.201558096565974</v>
       </c>
       <c r="E61">
-        <v>-15.3317857944997</v>
+        <v>-17.61255501921989</v>
       </c>
       <c r="F61">
-        <v>6.442324973923625</v>
+        <v>6.552057147037671</v>
       </c>
       <c r="G61">
-        <v>-10.25934457260663</v>
+        <v>-10.3141153833836</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.272969893260718</v>
       </c>
       <c r="E62">
-        <v>-15.15333891671712</v>
+        <v>-18.37603985706312</v>
       </c>
       <c r="F62">
-        <v>6.124984048850357</v>
+        <v>6.420490865920636</v>
       </c>
       <c r="G62">
-        <v>-10.55640553516186</v>
+        <v>-10.4793650730227</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.339430756640891</v>
       </c>
       <c r="E63">
-        <v>-13.82660801863461</v>
+        <v>-17.79074855111166</v>
       </c>
       <c r="F63">
-        <v>5.98483588144032</v>
+        <v>6.774087775479633</v>
       </c>
       <c r="G63">
-        <v>-10.34066665587522</v>
+        <v>-10.45698577038768</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.398215582964705</v>
       </c>
       <c r="E64">
-        <v>-14.15302966270951</v>
+        <v>-17.31751919312672</v>
       </c>
       <c r="F64">
-        <v>6.353575347122492</v>
+        <v>6.499997569241333</v>
       </c>
       <c r="G64">
-        <v>-10.98287196949251</v>
+        <v>-11.3237790820832</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.451482798934352</v>
       </c>
       <c r="E65">
-        <v>-13.50402809503518</v>
+        <v>-17.82375412151007</v>
       </c>
       <c r="F65">
-        <v>5.53853637583403</v>
+        <v>6.694286173363539</v>
       </c>
       <c r="G65">
-        <v>-10.23622381850773</v>
+        <v>-10.88301751574391</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.497041672950131</v>
       </c>
       <c r="E66">
-        <v>-13.70960790240287</v>
+        <v>-17.02357150840066</v>
       </c>
       <c r="F66">
-        <v>5.769743658364206</v>
+        <v>6.818458447043185</v>
       </c>
       <c r="G66">
-        <v>-10.09250885562842</v>
+        <v>-10.97822876023722</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.536945106529032</v>
       </c>
       <c r="E67">
-        <v>-14.63174956606587</v>
+        <v>-17.25301151482948</v>
       </c>
       <c r="F67">
-        <v>6.511621220637415</v>
+        <v>6.696052252666308</v>
       </c>
       <c r="G67">
-        <v>-10.39467121311469</v>
+        <v>-11.3549487617565</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.571334987158409</v>
       </c>
       <c r="E68">
-        <v>-13.78721896242994</v>
+        <v>-17.5922333562075</v>
       </c>
       <c r="F68">
-        <v>6.088996455403135</v>
+        <v>6.730542157849269</v>
       </c>
       <c r="G68">
-        <v>-10.60182465881346</v>
+        <v>-11.32361721591855</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.602410422841988</v>
       </c>
       <c r="E69">
-        <v>-13.15747583566884</v>
+        <v>-16.86402174214604</v>
       </c>
       <c r="F69">
-        <v>5.598589699067383</v>
+        <v>6.74370988608417</v>
       </c>
       <c r="G69">
-        <v>-11.01948635701058</v>
+        <v>-11.4098579419968</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.634083467761019</v>
       </c>
       <c r="E70">
-        <v>-14.91822562361857</v>
+        <v>-15.73122920008773</v>
       </c>
       <c r="F70">
-        <v>6.140421503768929</v>
+        <v>7.091991990386805</v>
       </c>
       <c r="G70">
-        <v>-10.36412550139867</v>
+        <v>-10.73096644538518</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.666029545502909</v>
       </c>
       <c r="E71">
-        <v>-12.73223268133097</v>
+        <v>-16.60916408240927</v>
       </c>
       <c r="F71">
-        <v>6.343727715438011</v>
+        <v>6.832484363907387</v>
       </c>
       <c r="G71">
-        <v>-10.51160385260606</v>
+        <v>-11.61798519542805</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.703829278231498</v>
       </c>
       <c r="E72">
-        <v>-14.09109697543367</v>
+        <v>-16.10469426883897</v>
       </c>
       <c r="F72">
-        <v>6.139818452299691</v>
+        <v>6.946765930797607</v>
       </c>
       <c r="G72">
-        <v>-10.73718132288432</v>
+        <v>-11.29609866255592</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.747012257343133</v>
       </c>
       <c r="E73">
-        <v>-13.4418711343478</v>
+        <v>-16.65511105929584</v>
       </c>
       <c r="F73">
-        <v>6.016545785619485</v>
+        <v>6.746581007502273</v>
       </c>
       <c r="G73">
-        <v>-10.33976594899128</v>
+        <v>-11.46722383289733</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.79976209596067</v>
       </c>
       <c r="E74">
-        <v>-14.74418114984031</v>
+        <v>-15.83761370817322</v>
       </c>
       <c r="F74">
-        <v>6.108305699562392</v>
+        <v>6.627731822753017</v>
       </c>
       <c r="G74">
-        <v>-11.25551724863166</v>
+        <v>-11.42490366307538</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.860954787043765</v>
       </c>
       <c r="E75">
-        <v>-14.54934570016995</v>
+        <v>-15.87600599365993</v>
       </c>
       <c r="F75">
-        <v>5.345362754235992</v>
+        <v>6.79959320781183</v>
       </c>
       <c r="G75">
-        <v>-10.6485830944403</v>
+        <v>-11.88521970640211</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.93191554037149</v>
       </c>
       <c r="E76">
-        <v>-14.62664111613634</v>
+        <v>-16.5271713844345</v>
       </c>
       <c r="F76">
-        <v>5.65525002941887</v>
+        <v>6.800651861352607</v>
       </c>
       <c r="G76">
-        <v>-11.6203205064648</v>
+        <v>-11.58838457325401</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.011888208135863</v>
       </c>
       <c r="E77">
-        <v>-14.00372171558193</v>
+        <v>-17.55094628242739</v>
       </c>
       <c r="F77">
-        <v>5.552096750217858</v>
+        <v>6.38709109223976</v>
       </c>
       <c r="G77">
-        <v>-9.75276352438078</v>
+        <v>-11.15748901072454</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.09672895794844</v>
       </c>
       <c r="E78">
-        <v>-15.20635881248988</v>
+        <v>-17.39083998585524</v>
       </c>
       <c r="F78">
-        <v>5.428645156178648</v>
+        <v>6.759435612858915</v>
       </c>
       <c r="G78">
-        <v>-10.02393895431513</v>
+        <v>-10.7970013137005</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.187202058807533</v>
       </c>
       <c r="E79">
-        <v>-17.13718675740267</v>
+        <v>-17.49823787750399</v>
       </c>
       <c r="F79">
-        <v>5.565499734795154</v>
+        <v>6.594892025436432</v>
       </c>
       <c r="G79">
-        <v>-9.850747379629853</v>
+        <v>-10.63058723197376</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.27805580555017</v>
       </c>
       <c r="E80">
-        <v>-15.66380596744047</v>
+        <v>-17.48358119473867</v>
       </c>
       <c r="F80">
-        <v>5.939389988987934</v>
+        <v>6.692375958132684</v>
       </c>
       <c r="G80">
-        <v>-9.81207833611858</v>
+        <v>-10.46984499287121</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.370102514319782</v>
       </c>
       <c r="E81">
-        <v>-15.37958510363715</v>
+        <v>-18.83168867151006</v>
       </c>
       <c r="F81">
-        <v>6.049165237206924</v>
+        <v>6.513982067735394</v>
       </c>
       <c r="G81">
-        <v>-9.89569395851046</v>
+        <v>-10.08594805447095</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.459165472336759</v>
       </c>
       <c r="E82">
-        <v>-18.06397586453816</v>
+        <v>-19.41604135170211</v>
       </c>
       <c r="F82">
-        <v>5.515033935881803</v>
+        <v>6.626724527991212</v>
       </c>
       <c r="G82">
-        <v>-10.17261041580066</v>
+        <v>-10.49645239637154</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.545233385190216</v>
       </c>
       <c r="E83">
-        <v>-18.0786533133601</v>
+        <v>-19.90236993820556</v>
       </c>
       <c r="F83">
-        <v>5.141209951081247</v>
+        <v>6.556488912642648</v>
       </c>
       <c r="G83">
-        <v>-9.579297821513441</v>
+        <v>-10.48777036523379</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.624792146409139</v>
       </c>
       <c r="E84">
-        <v>-19.637478119908</v>
+        <v>-21.12495490910666</v>
       </c>
       <c r="F84">
-        <v>5.465658268470535</v>
+        <v>6.477245630156041</v>
       </c>
       <c r="G84">
-        <v>-8.50963399062087</v>
+        <v>-10.28849353596641</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.695031357969659</v>
       </c>
       <c r="E85">
-        <v>-20.13676472574491</v>
+        <v>-21.72695458421791</v>
       </c>
       <c r="F85">
-        <v>6.073502671501173</v>
+        <v>6.710457561800991</v>
       </c>
       <c r="G85">
-        <v>-9.890230975453555</v>
+        <v>-9.972102620458573</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.754150562423142</v>
       </c>
       <c r="E86">
-        <v>-21.10911871432509</v>
+        <v>-22.56971176661814</v>
       </c>
       <c r="F86">
-        <v>5.426706776456097</v>
+        <v>6.766607617832354</v>
       </c>
       <c r="G86">
-        <v>-9.462541407281968</v>
+        <v>-9.992902422615972</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.796317763417918</v>
       </c>
       <c r="E87">
-        <v>-23.37489484616265</v>
+        <v>-23.62694078183252</v>
       </c>
       <c r="F87">
-        <v>5.760863559806196</v>
+        <v>6.37374609338066</v>
       </c>
       <c r="G87">
-        <v>-10.08403960017485</v>
+        <v>-9.985566230314944</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.819293973978668</v>
       </c>
       <c r="E88">
-        <v>-23.86202084924047</v>
+        <v>-24.7496410203715</v>
       </c>
       <c r="F88">
-        <v>5.382299656726821</v>
+        <v>6.833801468077838</v>
       </c>
       <c r="G88">
-        <v>-8.36779093161339</v>
+        <v>-9.927722573154238</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.815076852198342</v>
       </c>
       <c r="E89">
-        <v>-24.53396475627315</v>
+        <v>-25.67203602992532</v>
       </c>
       <c r="F89">
-        <v>5.803085446326886</v>
+        <v>6.578430708408001</v>
       </c>
       <c r="G89">
-        <v>-8.410310823396555</v>
+        <v>-9.692142034975131</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.779643056853589</v>
       </c>
       <c r="E90">
-        <v>-27.59981967093701</v>
+        <v>-28.20906254659876</v>
       </c>
       <c r="F90">
-        <v>5.788741436380009</v>
+        <v>6.793254540445608</v>
       </c>
       <c r="G90">
-        <v>-8.58827353382209</v>
+        <v>-9.197426820915892</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.701815141636692</v>
       </c>
       <c r="E91">
-        <v>-28.73333487176584</v>
+        <v>-29.03582155897575</v>
       </c>
       <c r="F91">
-        <v>6.140317129476176</v>
+        <v>6.859209153056504</v>
       </c>
       <c r="G91">
-        <v>-8.247496958460959</v>
+        <v>-9.374507099669628</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.57711437234386</v>
       </c>
       <c r="E92">
-        <v>-29.89669712578055</v>
+        <v>-30.71066009406575</v>
       </c>
       <c r="F92">
-        <v>4.832160983710002</v>
+        <v>6.56132160807058</v>
       </c>
       <c r="G92">
-        <v>-8.17041733515293</v>
+        <v>-9.615844329672141</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.396532791657305</v>
       </c>
       <c r="E93">
-        <v>-32.56963125324202</v>
+        <v>-32.53937095552931</v>
       </c>
       <c r="F93">
-        <v>5.322330826968554</v>
+        <v>6.46574954733999</v>
       </c>
       <c r="G93">
-        <v>-8.830420094647845</v>
+        <v>-9.402952467362104</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.155824433942028</v>
       </c>
       <c r="E94">
-        <v>-33.68750546022154</v>
+        <v>-34.21560704623011</v>
       </c>
       <c r="F94">
-        <v>5.077617842303135</v>
+        <v>6.221386133718553</v>
       </c>
       <c r="G94">
-        <v>-9.26535839517666</v>
+        <v>-9.049768328331707</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.85489688324023</v>
       </c>
       <c r="E95">
-        <v>-35.95484735272856</v>
+        <v>-37.46924525773477</v>
       </c>
       <c r="F95">
-        <v>5.215849167543094</v>
+        <v>6.265751835077689</v>
       </c>
       <c r="G95">
-        <v>-8.421702807419878</v>
+        <v>-9.066454902385807</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.49359295784517</v>
       </c>
       <c r="E96">
-        <v>-39.3469204041124</v>
+        <v>-37.90717231945867</v>
       </c>
       <c r="F96">
-        <v>4.913856233708895</v>
+        <v>6.317702068376857</v>
       </c>
       <c r="G96">
-        <v>-7.970649685902419</v>
+        <v>-9.145817621838765</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.085319575467626</v>
       </c>
       <c r="E97">
-        <v>-39.97270552048094</v>
+        <v>-41.91099678614444</v>
       </c>
       <c r="F97">
-        <v>4.862779099652277</v>
+        <v>6.181737156350957</v>
       </c>
       <c r="G97">
-        <v>-7.886342216193893</v>
+        <v>-8.598288350073599</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.632451849561333</v>
       </c>
       <c r="E98">
-        <v>-43.72695936544645</v>
+        <v>-43.55149657000076</v>
       </c>
       <c r="F98">
-        <v>4.986790670055781</v>
+        <v>5.833554456136658</v>
       </c>
       <c r="G98">
-        <v>-7.203937962734929</v>
+        <v>-9.310260591399217</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.165696848645632</v>
       </c>
       <c r="E99">
-        <v>-46.3003783963537</v>
+        <v>-45.61940021638668</v>
       </c>
       <c r="F99">
-        <v>4.602948409885768</v>
+        <v>5.998364777862841</v>
       </c>
       <c r="G99">
-        <v>-8.484466412762538</v>
+        <v>-8.896107733932553</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.686286239065562</v>
       </c>
       <c r="E100">
-        <v>-48.92735101068895</v>
+        <v>-47.46408121369705</v>
       </c>
       <c r="F100">
-        <v>4.879457448940243</v>
+        <v>5.444351002135726</v>
       </c>
       <c r="G100">
-        <v>-7.267164975242511</v>
+        <v>-8.618551644217526</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.244193552838845</v>
       </c>
       <c r="E101">
-        <v>-50.75418565893653</v>
+        <v>-50.24645038296208</v>
       </c>
       <c r="F101">
-        <v>4.588231634607632</v>
+        <v>5.220771326650529</v>
       </c>
       <c r="G101">
-        <v>-8.729647964175465</v>
+        <v>-8.926021645457528</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.820719549222217</v>
       </c>
       <c r="E102">
-        <v>-52.73498608081248</v>
+        <v>-52.94835938923121</v>
       </c>
       <c r="F102">
-        <v>3.773089945761223</v>
+        <v>5.251490503415946</v>
       </c>
       <c r="G102">
-        <v>-8.236743301490163</v>
+        <v>-8.638398524599168</v>
       </c>
     </row>
   </sheetData>
